--- a/examples/excel/charts/charts-bar.xlsx
+++ b/examples/excel/charts/charts-bar.xlsx
@@ -3,12 +3,13 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Bar Fundamentals" sheetId="2" r:id="R5c606f3073374b1b"/>
-    <x:sheet name="2-Bar Variants" sheetId="3" r:id="Rcf137e8ac3d84242"/>
-    <x:sheet name="3-Bar Styling" sheetId="4" r:id="Rdaf3aa092941470d"/>
-    <x:sheet name="4-Axis &amp; Labels" sheetId="5" r:id="R7a318a00e4f34402"/>
-    <x:sheet name="5-Legend &amp; Layout" sheetId="6" r:id="R8a3040b2c60446df"/>
-    <x:sheet name="6-Advanced" sheetId="7" r:id="Re7f78761ed5b497b"/>
+    <x:sheet name="1-Bar Fundamentals" sheetId="2" r:id="R3c7357a1075343dc"/>
+    <x:sheet name="2-Bar Variants" sheetId="3" r:id="Rf501798049964b9f"/>
+    <x:sheet name="3-Bar Styling" sheetId="4" r:id="R4b7d0b0dcee442f7"/>
+    <x:sheet name="4-Axis &amp; Labels" sheetId="5" r:id="Rdfda3a548210427a"/>
+    <x:sheet name="5-Legend &amp; Layout" sheetId="6" r:id="R620f4ebabce34d3a"/>
+    <x:sheet name="6-Advanced" sheetId="7" r:id="R9b9d9b76c660453d"/>
+    <x:sheet name="7-Axis Controls" sheetId="8" r:id="R2cb49e30fbb7448b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1408,6 +1409,18 @@
           </c:spPr>
           <c:dLbls>
             <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="3"/>
               <c:tx>
                 <c:rich>
@@ -2890,7 +2903,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -3258,7 +3271,7 @@
             <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="900" b="0">
+                <a:defRPr sz="900">
                   <a:solidFill>
                     <a:srgbClr val="333333"/>
                   </a:solidFill>
@@ -4066,6 +4079,639 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Axis Cross Controls</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sales</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>-30</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>150</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Tick-label Rotation, Offset &amp; Skip</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Units</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>January</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>February</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>March</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>April</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>May</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>June</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>July</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>20</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>60</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="2700000"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr/>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="2"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="2700000"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr/>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Stacked — axisposition + serlines</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Online</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>70</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Retail</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>25</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:serLines/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Line — markercolor</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sales</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>145</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>132</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>160</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Costs</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>95</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>88</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>110</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:chart>
@@ -5073,6 +5719,7 @@
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -5106,6 +5753,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -5251,9 +5907,10 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="60"/>
+        <c:shape val="cylinder"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:shape val="cylinder"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -5287,6 +5944,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -5445,7 +6111,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rabf3f49a7b3245dd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf47618ed2df445a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5475,7 +6141,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4a8947a2ff3439e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R586eb1d9f5fa4464"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5505,7 +6171,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf317c581fd74f56"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8c12c1ae9b34acb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5535,7 +6201,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6e12ad1a9844ff9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R535d8cd2319441ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5570,7 +6236,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc36a856756294e77"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Recad7fc115864fb6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5600,7 +6266,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd766c2bb998492f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rafaf7e6c78f34133"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5630,7 +6296,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57a0dd5352814da9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf5db51d1e3af45b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5660,7 +6326,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7c231f2bc834854"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4fa80bbee41343dc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5695,7 +6361,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3dc0ea24c60c4a98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51f09d79b4014feb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5725,7 +6391,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R950846bb3714448d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21bbf5d7dd9a4c84"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5755,7 +6421,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c992df0fa1d4173"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2bae37cd25e84a9e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5785,7 +6451,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R49f970d8dcdd404c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra93ce9a331034454"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5820,7 +6486,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50abb13863e24191"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfacbcb10dc0a4d0e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5850,7 +6516,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2ccd262267f145a5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0ad51e3ac424629"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5880,7 +6546,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6fcf5e63ea044072"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R895cd07eeb5f48e9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5910,7 +6576,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc7f8b5ff6ed6490e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb833de32f7e24feb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5945,7 +6611,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f384dd8b7b34e64"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26e21e5c99f34ad3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5975,7 +6641,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20a3da6510ea4e80"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb25cdf9bf29b4867"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6005,7 +6671,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68c410a70cad43ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a013b58416f474c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6035,7 +6701,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb1c2f47056984118"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R962e9f65e0604c27"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6070,7 +6736,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red23fcb4bc2047ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e0ab2fb0fd84cc6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6100,7 +6766,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref11cea7e34241f3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb667e22d2424fd9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6130,7 +6796,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R509f880ee19a4daf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b1347a427c149b4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6160,7 +6826,132 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a2910080ee24bee"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R08336836eff747fa"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Axis Cross Controls"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73423736b4a74baf"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Tick-label Rotation, Offset &amp; Skip"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2529166c2624f3f"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Stacked — axisposition + serlines"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb612de8334640db"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Line — markercolor"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9ce6517dcd14f2f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6332,41 +7123,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d0e5fc75bc44cb9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a125bca8a940cf"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7440683498804ae3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3180c5387664b86"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59f1ad5139ab438b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R538bf1606923445a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b4b511aa3fe49a0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7493671fbe44f3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbb8463cad184acc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf32501666ff43b1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20f402f6e28943f0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafb1906616fc4ef8"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0776dacdc443ed"/>
 </x:worksheet>
 </file>